--- a/_producao-16-8/_resultados.xlsx
+++ b/_producao-16-8/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_producao-16-8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC03027-D1AB-4A4B-B7D2-2B5E561D4DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243385AC-9EE7-4C61-96E5-DD12CDF55039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="12">
   <si>
     <t>Estratégia</t>
   </si>
@@ -132,105 +132,6 @@
   </si>
   <si>
     <t>Gender</t>
-  </si>
-  <si>
-    <t>0.0012274070744325545</t>
-  </si>
-  <si>
-    <t>0.0015217850441141796</t>
-  </si>
-  <si>
-    <t>0.0014187702239963444</t>
-  </si>
-  <si>
-    <t>0.0012192305758858706</t>
-  </si>
-  <si>
-    <t>0.0012107251197056351</t>
-  </si>
-  <si>
-    <t>0.0015994412310248716</t>
-  </si>
-  <si>
-    <t>0.0013964272541872906</t>
-  </si>
-  <si>
-    <t>0.0015234914987065466</t>
-  </si>
-  <si>
-    <t>0.0011443291811593808</t>
-  </si>
-  <si>
-    <t>0.0012948013461969545</t>
-  </si>
-  <si>
-    <t>0.0011901786885313496</t>
-  </si>
-  <si>
-    <t>0.006849455033542327</t>
-  </si>
-  <si>
-    <t>0.0077222014481316</t>
-  </si>
-  <si>
-    <t>0.007427603295107875</t>
-  </si>
-  <si>
-    <t>0.006916364236332379</t>
-  </si>
-  <si>
-    <t>0.007124746848741523</t>
-  </si>
-  <si>
-    <t>0.007968352317679107</t>
-  </si>
-  <si>
-    <t>0.007132530470366947</t>
-  </si>
-  <si>
-    <t>0.0076723666731501675</t>
-  </si>
-  <si>
-    <t>0.006448644664668599</t>
-  </si>
-  <si>
-    <t>0.007199808666308339</t>
-  </si>
-  <si>
-    <t>0.006840864833693129</t>
-  </si>
-  <si>
-    <t>0.002813664709299093</t>
-  </si>
-  <si>
-    <t>0.002908629984365627</t>
-  </si>
-  <si>
-    <t>0.002872510923306513</t>
-  </si>
-  <si>
-    <t>0.00274722208660624</t>
-  </si>
-  <si>
-    <t>0.0028395079487722507</t>
-  </si>
-  <si>
-    <t>0.002909492750016782</t>
-  </si>
-  <si>
-    <t>0.0029300338678111223</t>
-  </si>
-  <si>
-    <t>0.002895450817767842</t>
-  </si>
-  <si>
-    <t>0.0028613029088541495</t>
-  </si>
-  <si>
-    <t>0.002883439457633324</t>
-  </si>
-  <si>
-    <t>0.0027874350825794992</t>
   </si>
 </sst>
 </file>
@@ -722,12 +623,12 @@
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="8" t="e">
+      <c r="D2" s="3">
+        <v>1.22740707443255E-3</v>
+      </c>
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D12)</f>
-        <v>#DIV/0!</v>
+        <v>1.3405988398128117E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -736,8 +637,8 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
+      <c r="D3" s="3">
+        <v>1.5217850441141701E-3</v>
       </c>
       <c r="E3" s="7"/>
     </row>
@@ -747,8 +648,8 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>14</v>
+      <c r="D4" s="3">
+        <v>1.4187702239963399E-3</v>
       </c>
       <c r="E4" s="7"/>
     </row>
@@ -758,8 +659,8 @@
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
+      <c r="D5" s="3">
+        <v>1.21923057588587E-3</v>
       </c>
       <c r="E5" s="7"/>
     </row>
@@ -769,8 +670,8 @@
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>16</v>
+      <c r="D6" s="3">
+        <v>1.2107251197056299E-3</v>
       </c>
       <c r="E6" s="7"/>
     </row>
@@ -780,8 +681,8 @@
       <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>17</v>
+      <c r="D7" s="3">
+        <v>1.5994412310248701E-3</v>
       </c>
       <c r="E7" s="7"/>
     </row>
@@ -791,8 +692,8 @@
       <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>18</v>
+      <c r="D8" s="3">
+        <v>1.3964272541872899E-3</v>
       </c>
       <c r="E8" s="7"/>
     </row>
@@ -802,8 +703,8 @@
       <c r="C9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>19</v>
+      <c r="D9" s="3">
+        <v>1.5234914987065399E-3</v>
       </c>
       <c r="E9" s="7"/>
     </row>
@@ -813,8 +714,8 @@
       <c r="C10" s="1">
         <v>9</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>20</v>
+      <c r="D10" s="3">
+        <v>1.14432918115938E-3</v>
       </c>
       <c r="E10" s="7"/>
     </row>
@@ -824,8 +725,8 @@
       <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>21</v>
+      <c r="D11" s="3">
+        <v>1.29480134619695E-3</v>
       </c>
       <c r="E11" s="7"/>
     </row>
@@ -835,8 +736,8 @@
       <c r="C12" s="1">
         <v>11</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>22</v>
+      <c r="D12" s="3">
+        <v>1.1901786885313401E-3</v>
       </c>
       <c r="E12" s="7"/>
     </row>
@@ -848,10 +749,12 @@
       <c r="C13" s="1">
         <v>1</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="12" t="e">
+      <c r="D13" s="3">
+        <v>1.76494351019696E-4</v>
+      </c>
+      <c r="E13" s="12">
         <f>AVERAGE(D13:D23)</f>
-        <v>#DIV/0!</v>
+        <v>4.6044642516324585E-4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -860,7 +763,9 @@
       <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3">
+        <v>5.46025356640438E-4</v>
+      </c>
       <c r="E14" s="13"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -869,7 +774,9 @@
       <c r="C15" s="1">
         <v>3</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>1.7489087688418899E-4</v>
+      </c>
       <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -878,7 +785,9 @@
       <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3">
+        <v>4.5331415788522699E-4</v>
+      </c>
       <c r="E16" s="13"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -887,7 +796,9 @@
       <c r="C17" s="1">
         <v>5</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3">
+        <v>4.5224030226177498E-4</v>
+      </c>
       <c r="E17" s="13"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -896,7 +807,9 @@
       <c r="C18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3">
+        <v>3.25042909349475E-4</v>
+      </c>
       <c r="E18" s="13"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -905,7 +818,9 @@
       <c r="C19" s="1">
         <v>7</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3">
+        <v>5.4759582523591596E-4</v>
+      </c>
       <c r="E19" s="13"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -914,7 +829,9 @@
       <c r="C20" s="1">
         <v>8</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3">
+        <v>4.0296400000000003E-5</v>
+      </c>
       <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -923,7 +840,9 @@
       <c r="C21" s="1">
         <v>9</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3">
+        <v>8.9001901515576199E-4</v>
+      </c>
       <c r="E21" s="13"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -932,7 +851,9 @@
       <c r="C22" s="1">
         <v>10</v>
       </c>
-      <c r="D22" s="3"/>
+      <c r="D22" s="3">
+        <v>8.6876944325313898E-4</v>
+      </c>
       <c r="E22" s="13"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -941,7 +862,9 @@
       <c r="C23" s="1">
         <v>11</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3">
+        <v>5.9022203911008697E-4</v>
+      </c>
       <c r="E23" s="14"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -952,10 +875,12 @@
       <c r="C24" s="1">
         <v>1</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="8" t="e">
+      <c r="D24" s="3">
+        <v>1.73793482370665E-4</v>
+      </c>
+      <c r="E24" s="8">
         <f>AVERAGE(D24:D33)</f>
-        <v>#DIV/0!</v>
+        <v>1.4431720299863652E-4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -964,7 +889,9 @@
       <c r="C25" s="1">
         <v>2</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3">
+        <v>4.4079599999999997E-5</v>
+      </c>
       <c r="E25" s="7"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -973,7 +900,9 @@
       <c r="C26" s="1">
         <v>3</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3">
+        <v>1.9820721733818201E-4</v>
+      </c>
       <c r="E26" s="7"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -982,7 +911,9 @@
       <c r="C27" s="1">
         <v>4</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="3">
+        <v>2.6898882604876098E-4</v>
+      </c>
       <c r="E27" s="7"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -991,7 +922,9 @@
       <c r="C28" s="1">
         <v>5</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3">
+        <v>9.9348000000000002E-6</v>
+      </c>
       <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1000,7 +933,9 @@
       <c r="C29" s="1">
         <v>6</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3">
+        <v>1.70899292234211E-4</v>
+      </c>
       <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1102,12 +1037,12 @@
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="8" t="e">
+      <c r="D2" s="3">
+        <v>6.8494550335423199E-3</v>
+      </c>
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D12)</f>
-        <v>#DIV/0!</v>
+        <v>7.2093580443383567E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1116,8 +1051,8 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>24</v>
+      <c r="D3" s="3">
+        <v>7.7222014481316001E-3</v>
       </c>
       <c r="E3" s="7"/>
     </row>
@@ -1127,8 +1062,8 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>25</v>
+      <c r="D4" s="3">
+        <v>7.4276032951078701E-3</v>
       </c>
       <c r="E4" s="7"/>
     </row>
@@ -1138,8 +1073,8 @@
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
+      <c r="D5" s="3">
+        <v>6.9163642363323698E-3</v>
       </c>
       <c r="E5" s="7"/>
     </row>
@@ -1149,8 +1084,8 @@
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
+      <c r="D6" s="3">
+        <v>7.1247468487415202E-3</v>
       </c>
       <c r="E6" s="7"/>
     </row>
@@ -1160,8 +1095,8 @@
       <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>28</v>
+      <c r="D7" s="3">
+        <v>7.9683523176790998E-3</v>
       </c>
       <c r="E7" s="7"/>
     </row>
@@ -1171,8 +1106,8 @@
       <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>29</v>
+      <c r="D8" s="3">
+        <v>7.1325304703669396E-3</v>
       </c>
       <c r="E8" s="7"/>
     </row>
@@ -1182,8 +1117,8 @@
       <c r="C9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>30</v>
+      <c r="D9" s="3">
+        <v>7.6723666731501597E-3</v>
       </c>
       <c r="E9" s="7"/>
     </row>
@@ -1193,8 +1128,8 @@
       <c r="C10" s="1">
         <v>9</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>31</v>
+      <c r="D10" s="3">
+        <v>6.44864466466859E-3</v>
       </c>
       <c r="E10" s="7"/>
     </row>
@@ -1204,8 +1139,8 @@
       <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>32</v>
+      <c r="D11" s="3">
+        <v>7.1998086663083299E-3</v>
       </c>
       <c r="E11" s="7"/>
     </row>
@@ -1215,8 +1150,8 @@
       <c r="C12" s="1">
         <v>11</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>33</v>
+      <c r="D12" s="3">
+        <v>6.8408648336931201E-3</v>
       </c>
       <c r="E12" s="7"/>
     </row>
@@ -1228,10 +1163,12 @@
       <c r="C13" s="1">
         <v>1</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="8" t="e">
+      <c r="D13" s="3">
+        <v>4.4059430113216501E-3</v>
+      </c>
+      <c r="E13" s="8">
         <f>AVERAGE(D13:D23)</f>
-        <v>#DIV/0!</v>
+        <v>5.6171193080640424E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1240,7 +1177,9 @@
       <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3">
+        <v>6.0285373262784596E-3</v>
+      </c>
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1249,7 +1188,9 @@
       <c r="C15" s="1">
         <v>3</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>4.6542086132795998E-3</v>
+      </c>
       <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1258,7 +1199,9 @@
       <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3">
+        <v>5.4842343524997596E-3</v>
+      </c>
       <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1267,7 +1210,9 @@
       <c r="C17" s="1">
         <v>5</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3">
+        <v>5.2386490268761304E-3</v>
+      </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1276,7 +1221,9 @@
       <c r="C18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3">
+        <v>4.5414210107642796E-3</v>
+      </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1285,7 +1232,9 @@
       <c r="C19" s="1">
         <v>7</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3">
+        <v>6.4272965329950603E-3</v>
+      </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1294,7 +1243,9 @@
       <c r="C20" s="1">
         <v>8</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3">
+        <v>3.38376634582825E-3</v>
+      </c>
       <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1303,7 +1254,9 @@
       <c r="C21" s="1">
         <v>9</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3">
+        <v>7.5523987537550697E-3</v>
+      </c>
       <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1312,7 +1265,9 @@
       <c r="C22" s="1">
         <v>10</v>
       </c>
-      <c r="D22" s="3"/>
+      <c r="D22" s="3">
+        <v>7.6800340233492996E-3</v>
+      </c>
       <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1321,7 +1276,9 @@
       <c r="C23" s="1">
         <v>11</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3">
+        <v>6.3918233917569199E-3</v>
+      </c>
       <c r="E23" s="7"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1332,10 +1289,12 @@
       <c r="C24" s="1">
         <v>1</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="8" t="e">
+      <c r="D24" s="3">
+        <v>6.8834568210915997E-3</v>
+      </c>
+      <c r="E24" s="8">
         <f>AVERAGE(D24:D33)</f>
-        <v>#DIV/0!</v>
+        <v>5.5388854668757303E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1344,7 +1303,9 @@
       <c r="C25" s="1">
         <v>2</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3">
+        <v>5.9727451086721804E-3</v>
+      </c>
       <c r="E25" s="7"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1353,7 +1314,9 @@
       <c r="C26" s="1">
         <v>3</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3">
+        <v>3.2861956035523401E-3</v>
+      </c>
       <c r="E26" s="7"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1362,7 +1325,9 @@
       <c r="C27" s="1">
         <v>4</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="3">
+        <v>4.1621944755989501E-3</v>
+      </c>
       <c r="E27" s="7"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1371,7 +1336,9 @@
       <c r="C28" s="1">
         <v>5</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3">
+        <v>6.0968354981954303E-3</v>
+      </c>
       <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1380,7 +1347,9 @@
       <c r="C29" s="1">
         <v>6</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3">
+        <v>6.8318852941438796E-3</v>
+      </c>
       <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1482,12 +1451,12 @@
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="8" t="e">
+      <c r="D2" s="3">
+        <v>2.81366470929909E-3</v>
+      </c>
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D12)</f>
-        <v>#DIV/0!</v>
+        <v>2.8589718670011272E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1496,8 +1465,8 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>35</v>
+      <c r="D3" s="3">
+        <v>2.9086299843656201E-3</v>
       </c>
       <c r="E3" s="7"/>
     </row>
@@ -1507,8 +1476,8 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>36</v>
+      <c r="D4" s="3">
+        <v>2.8725109233065098E-3</v>
       </c>
       <c r="E4" s="7"/>
     </row>
@@ -1518,8 +1487,8 @@
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>37</v>
+      <c r="D5" s="3">
+        <v>2.7472220866062401E-3</v>
       </c>
       <c r="E5" s="7"/>
     </row>
@@ -1529,8 +1498,8 @@
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>38</v>
+      <c r="D6" s="3">
+        <v>2.8395079487722498E-3</v>
       </c>
       <c r="E6" s="7"/>
     </row>
@@ -1540,8 +1509,8 @@
       <c r="C7" s="1">
         <v>6</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>39</v>
+      <c r="D7" s="3">
+        <v>2.9094927500167801E-3</v>
       </c>
       <c r="E7" s="7"/>
     </row>
@@ -1551,8 +1520,8 @@
       <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>40</v>
+      <c r="D8" s="3">
+        <v>2.9300338678111201E-3</v>
       </c>
       <c r="E8" s="7"/>
     </row>
@@ -1562,8 +1531,8 @@
       <c r="C9" s="1">
         <v>8</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>41</v>
+      <c r="D9" s="3">
+        <v>2.8954508177678399E-3</v>
       </c>
       <c r="E9" s="7"/>
     </row>
@@ -1573,8 +1542,8 @@
       <c r="C10" s="1">
         <v>9</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>42</v>
+      <c r="D10" s="3">
+        <v>2.86130290885414E-3</v>
       </c>
       <c r="E10" s="7"/>
     </row>
@@ -1584,8 +1553,8 @@
       <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>43</v>
+      <c r="D11" s="3">
+        <v>2.8834394576333199E-3</v>
       </c>
       <c r="E11" s="7"/>
     </row>
@@ -1595,8 +1564,8 @@
       <c r="C12" s="1">
         <v>11</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>44</v>
+      <c r="D12" s="3">
+        <v>2.7874350825794901E-3</v>
       </c>
       <c r="E12" s="7"/>
     </row>
@@ -1608,10 +1577,12 @@
       <c r="C13" s="1">
         <v>1</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="8" t="e">
+      <c r="D13" s="3">
+        <v>2.4381599990933901E-3</v>
+      </c>
+      <c r="E13" s="8">
         <f>AVERAGE(D13:D23)</f>
-        <v>#DIV/0!</v>
+        <v>2.6530523100631071E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1620,7 +1591,9 @@
       <c r="C14" s="1">
         <v>2</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3">
+        <v>2.6282434237133502E-3</v>
+      </c>
       <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1629,7 +1602,9 @@
       <c r="C15" s="1">
         <v>3</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>2.3461147455381701E-3</v>
+      </c>
       <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1638,7 +1613,9 @@
       <c r="C16" s="1">
         <v>4</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3">
+        <v>2.7524372879068298E-3</v>
+      </c>
       <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1647,7 +1624,9 @@
       <c r="C17" s="1">
         <v>5</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3">
+        <v>3.2472745789499402E-3</v>
+      </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1656,7 +1635,9 @@
       <c r="C18" s="1">
         <v>6</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3">
+        <v>2.5237854282296E-3</v>
+      </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1665,7 +1646,9 @@
       <c r="C19" s="1">
         <v>7</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3">
+        <v>2.9887873260404599E-3</v>
+      </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1674,7 +1657,9 @@
       <c r="C20" s="1">
         <v>8</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3">
+        <v>2.06526349558706E-3</v>
+      </c>
       <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1683,7 +1668,9 @@
       <c r="C21" s="1">
         <v>9</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3">
+        <v>2.6816447983030599E-3</v>
+      </c>
       <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1692,7 +1679,9 @@
       <c r="C22" s="1">
         <v>10</v>
       </c>
-      <c r="D22" s="3"/>
+      <c r="D22" s="3">
+        <v>2.7565596821078398E-3</v>
+      </c>
       <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1701,7 +1690,9 @@
       <c r="C23" s="1">
         <v>11</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3">
+        <v>2.7553046452244798E-3</v>
+      </c>
       <c r="E23" s="7"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1712,10 +1703,12 @@
       <c r="C24" s="1">
         <v>1</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="8" t="e">
+      <c r="D24" s="3">
+        <v>3.3099004965032601E-3</v>
+      </c>
+      <c r="E24" s="8">
         <f>AVERAGE(D24:D33)</f>
-        <v>#DIV/0!</v>
+        <v>2.3929610374087882E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1724,7 +1717,9 @@
       <c r="C25" s="1">
         <v>2</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3">
+        <v>2.0223762558382102E-3</v>
+      </c>
       <c r="E25" s="7"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1733,7 +1728,9 @@
       <c r="C26" s="1">
         <v>3</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3">
+        <v>2.48460504443907E-3</v>
+      </c>
       <c r="E26" s="7"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1742,7 +1739,9 @@
       <c r="C27" s="1">
         <v>4</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="3">
+        <v>2.1925517311301699E-3</v>
+      </c>
       <c r="E27" s="7"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1751,7 +1750,9 @@
       <c r="C28" s="1">
         <v>5</v>
       </c>
-      <c r="D28" s="3"/>
+      <c r="D28" s="3">
+        <v>2.0210547846704601E-3</v>
+      </c>
       <c r="E28" s="7"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1760,7 +1761,9 @@
       <c r="C29" s="1">
         <v>6</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3">
+        <v>2.32727791187156E-3</v>
+      </c>
       <c r="E29" s="7"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">

--- a/_producao-16-8/_resultados.xlsx
+++ b/_producao-16-8/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_producao-16-8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243385AC-9EE7-4C61-96E5-DD12CDF55039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C85165-0FBC-42F8-BDA5-EBDC4FD19A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="E24" s="8">
         <f>AVERAGE(D24:D33)</f>
-        <v>1.4431720299863652E-4</v>
+        <v>2.0032376576300951E-4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -944,7 +944,9 @@
       <c r="C30" s="1">
         <v>7</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3">
+        <v>3.7644454634369102E-4</v>
+      </c>
       <c r="E30" s="7"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -953,7 +955,9 @@
       <c r="C31" s="1">
         <v>8</v>
       </c>
-      <c r="D31" s="3"/>
+      <c r="D31" s="3">
+        <v>7.5758852866904895E-5</v>
+      </c>
       <c r="E31" s="7"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -962,7 +966,9 @@
       <c r="C32" s="1">
         <v>9</v>
       </c>
-      <c r="D32" s="3"/>
+      <c r="D32" s="3">
+        <v>4.9271851899704603E-4</v>
+      </c>
       <c r="E32" s="7"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -971,7 +977,9 @@
       <c r="C33" s="1">
         <v>10</v>
       </c>
-      <c r="D33" s="3"/>
+      <c r="D33" s="3">
+        <v>1.9241252143063401E-4</v>
+      </c>
       <c r="E33" s="7"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1294,7 +1302,7 @@
       </c>
       <c r="E24" s="8">
         <f>AVERAGE(D24:D33)</f>
-        <v>5.5388854668757303E-3</v>
+        <v>4.7018859667192891E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1358,7 +1366,9 @@
       <c r="C30" s="1">
         <v>7</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3">
+        <v>3.3675964367588002E-3</v>
+      </c>
       <c r="E30" s="7"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1367,7 +1377,9 @@
       <c r="C31" s="1">
         <v>8</v>
       </c>
-      <c r="D31" s="3"/>
+      <c r="D31" s="3">
+        <v>2.7372032922601602E-3</v>
+      </c>
       <c r="E31" s="7"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1376,7 +1388,9 @@
       <c r="C32" s="1">
         <v>9</v>
       </c>
-      <c r="D32" s="3"/>
+      <c r="D32" s="3">
+        <v>4.0609534836609498E-3</v>
+      </c>
       <c r="E32" s="7"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1385,7 +1399,9 @@
       <c r="C33" s="1">
         <v>10</v>
       </c>
-      <c r="D33" s="3"/>
+      <c r="D33" s="3">
+        <v>3.6197936532585901E-3</v>
+      </c>
       <c r="E33" s="7"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1708,7 +1724,7 @@
       </c>
       <c r="E24" s="8">
         <f>AVERAGE(D24:D33)</f>
-        <v>2.3929610374087882E-3</v>
+        <v>2.4948066730810809E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1772,7 +1788,9 @@
       <c r="C30" s="1">
         <v>7</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3">
+        <v>3.3527282363668498E-3</v>
+      </c>
       <c r="E30" s="7"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1781,7 +1799,9 @@
       <c r="C31" s="1">
         <v>8</v>
       </c>
-      <c r="D31" s="3"/>
+      <c r="D31" s="3">
+        <v>2.00939520752292E-3</v>
+      </c>
       <c r="E31" s="7"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1790,7 +1810,9 @@
       <c r="C32" s="1">
         <v>9</v>
       </c>
-      <c r="D32" s="3"/>
+      <c r="D32" s="3">
+        <v>2.9226176336739399E-3</v>
+      </c>
       <c r="E32" s="7"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1799,7 +1821,9 @@
       <c r="C33" s="1">
         <v>10</v>
       </c>
-      <c r="D33" s="3"/>
+      <c r="D33" s="3">
+        <v>2.3055594287943698E-3</v>
+      </c>
       <c r="E33" s="7"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">

--- a/_producao-16-8/_resultados.xlsx
+++ b/_producao-16-8/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_producao-16-8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C85165-0FBC-42F8-BDA5-EBDC4FD19A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE3327B-F71B-44AF-AECF-33C203E6475C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>

--- a/_producao-16-8/_resultados.xlsx
+++ b/_producao-16-8/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_producao-16-8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE3327B-F71B-44AF-AECF-33C203E6475C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B7BCC4-3BC6-484F-9C3C-217108D67E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="E32" s="7"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="1">
@@ -1825,8 +1825,11 @@
         <v>2.3055594287943698E-3</v>
       </c>
       <c r="E33" s="7"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="G33" s="4">
+        <v>2.3055594287943698E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>5</v>
       </c>

--- a/_producao-16-8/_resultados.xlsx
+++ b/_producao-16-8/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_producao-16-8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B7BCC4-3BC6-484F-9C3C-217108D67E04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE28B083-79E1-4540-A878-90C93A761F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -587,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70966A2D-672A-451B-A3A3-B783FCE2984F}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -879,8 +879,8 @@
         <v>1.73793482370665E-4</v>
       </c>
       <c r="E24" s="8">
-        <f>AVERAGE(D24:D33)</f>
-        <v>2.0032376576300951E-4</v>
+        <f>AVERAGE(D24:D37)</f>
+        <v>2.1330410891497666E-4</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -982,23 +982,67 @@
       </c>
       <c r="E33" s="7"/>
     </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="1">
+        <v>11</v>
+      </c>
+      <c r="D34" s="3">
+        <v>3.3565148161274601E-4</v>
+      </c>
+      <c r="E34" s="7"/>
+    </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="1">
+        <v>12</v>
+      </c>
+      <c r="D35" s="3">
+        <v>1.2738871373007399E-4</v>
+      </c>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="1">
+        <v>13</v>
+      </c>
+      <c r="D36" s="3">
+        <v>3.4164426510307702E-4</v>
+      </c>
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="1">
+        <v>14</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1.78335406733681E-4</v>
+      </c>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A2:A37"/>
     <mergeCell ref="B2:B12"/>
     <mergeCell ref="E2:E12"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="E24:E33"/>
+    <mergeCell ref="B24:B37"/>
+    <mergeCell ref="E24:E37"/>
     <mergeCell ref="B13:B23"/>
     <mergeCell ref="E13:E23"/>
   </mergeCells>
